--- a/backend/data/financials_by_company/0CY.F.xlsx
+++ b/backend/data/financials_by_company/0CY.F.xlsx
@@ -4331,10 +4331,8 @@
           <t>VR</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>37015</t>
-        </is>
+      <c r="E2" t="n">
+        <v>37015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
